--- a/evidence/s03c4/browser_visual/download.xlsx
+++ b/evidence/s03c4/browser_visual/download.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>089af204cb655eeb0b6adf7c62a20db6</t>
+    <t>24ee76fb7b67582ec6e45bbddc4fd697</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>2a766f7b060b47c7d550d0f114e029f5</t>
+    <t>bc82629005e6850939a619b392bd85d8</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T21:08:20-06:00</t>
+    <t>2026-10-26T21:13:50-06:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03c4/browser_visual/download.xlsx
+++ b/evidence/s03c4/browser_visual/download.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>24ee76fb7b67582ec6e45bbddc4fd697</t>
+    <t>45303e46829cc7142295cc468e4835f1</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>bc82629005e6850939a619b392bd85d8</t>
+    <t>6608392d539f63c0d2ab87134a731439</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T21:13:50-06:00</t>
+    <t>2026-10-26T21:22:43-06:00</t>
   </si>
   <si>
     <t>precision</t>
